--- a/Metadata_Converter/template.xlsx
+++ b/Metadata_Converter/template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qustj\OneDrive\바탕 화면\M.AX 추진단\제조데이터 현황판\수집체계\제출 샘플 제작\불량검출\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qustj\OneDrive\바탕 화면\M.AX 추진단\제조데이터 현황판\수집체계\제출 샘플 제작\v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F42837E-5E7A-4C4C-B2A9-9EAB42B82F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A8C4F3-9205-4546-ADF9-23E859D2FE7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="기본정보" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="113">
   <si>
     <t>구분</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -473,6 +473,27 @@
   <si>
     <t>Object Detection</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>라벨 컬럼</t>
+  </si>
+  <si>
+    <t>라벨로 사용하는 컬럼명 또는 인덱스
+(컬럼 기반 매핑 시)</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>데이터-라벨 매핑이 'column', 'id/key'일 때 필수.
+파일명 기반 매핑이면 공란.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>column: 데이터와 같은 행(레코드)에 라벨
+filename: 파일명으로 매칭
+id/key: 식별자 컬럼으로 조인
+index: 저장 순서(i번째↔i번째)로 매칭</t>
   </si>
 </sst>
 </file>
@@ -671,7 +692,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -729,6 +750,21 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -736,19 +772,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1041,13 +1065,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
     </row>
     <row r="2" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
@@ -1076,7 +1100,7 @@
       <c r="C3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="21" t="s">
         <v>38</v>
       </c>
       <c r="E3" s="14"/>
@@ -1091,7 +1115,7 @@
       <c r="C4" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="21" t="s">
         <v>37</v>
       </c>
       <c r="E4" s="14"/>
@@ -1106,7 +1130,7 @@
       <c r="C5" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="21" t="s">
         <v>36</v>
       </c>
       <c r="E5" s="14"/>
@@ -1121,7 +1145,7 @@
       <c r="C6" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="21" t="s">
         <v>35</v>
       </c>
       <c r="E6" s="14"/>
@@ -1136,7 +1160,7 @@
       <c r="C7" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="21" t="s">
         <v>34</v>
       </c>
       <c r="E7" s="14"/>
@@ -1151,7 +1175,7 @@
       <c r="C8" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="21" t="s">
         <v>33</v>
       </c>
       <c r="E8" s="15" t="s">
@@ -1168,7 +1192,7 @@
       <c r="C9" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="22" t="s">
         <v>29</v>
       </c>
       <c r="E9" s="14"/>
@@ -1183,7 +1207,7 @@
       <c r="C10" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="22" t="s">
         <v>30</v>
       </c>
       <c r="E10" s="14"/>
@@ -1198,7 +1222,7 @@
       <c r="C11" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" s="23" t="s">
         <v>31</v>
       </c>
       <c r="E11" s="14"/>
@@ -1213,7 +1237,7 @@
       <c r="C12" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="21" t="s">
         <v>32</v>
       </c>
       <c r="E12" s="14"/>
@@ -1228,7 +1252,7 @@
       <c r="C13" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="26" t="s">
+      <c r="D13" s="24" t="s">
         <v>101</v>
       </c>
       <c r="E13" s="20" t="s">
@@ -1245,7 +1269,7 @@
       <c r="C14" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="25">
         <v>46272</v>
       </c>
       <c r="E14" s="14"/>
@@ -1281,13 +1305,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
     </row>
     <row r="2" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -1316,7 +1340,7 @@
       <c r="C3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="21" t="s">
         <v>106</v>
       </c>
       <c r="E3" s="7"/>
@@ -1331,7 +1355,7 @@
       <c r="C4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="21" t="s">
         <v>103</v>
       </c>
       <c r="E4" s="7"/>
@@ -1346,7 +1370,7 @@
       <c r="C5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="21" t="s">
         <v>44</v>
       </c>
       <c r="E5" s="7"/>
@@ -1361,7 +1385,7 @@
       <c r="C6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="21" t="s">
         <v>45</v>
       </c>
       <c r="E6" s="7"/>
@@ -1376,7 +1400,7 @@
       <c r="C7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="21" t="s">
         <v>46</v>
       </c>
       <c r="E7" s="10" t="s">
@@ -1399,24 +1423,24 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{198A0CCE-64CE-4AF3-8AFB-53C70BC36516}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.375" customWidth="1"/>
     <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="37.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
     </row>
     <row r="2" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -1445,7 +1469,7 @@
       <c r="C3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="21" t="s">
         <v>56</v>
       </c>
       <c r="E3" s="7"/>
@@ -1460,7 +1484,7 @@
       <c r="C4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="21" t="s">
         <v>104</v>
       </c>
       <c r="E4" s="7"/>
@@ -1475,12 +1499,12 @@
       <c r="C5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="21" t="s">
         <v>59</v>
       </c>
       <c r="E5" s="7"/>
     </row>
-    <row r="6" spans="1:5" ht="27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="66" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>60</v>
       </c>
@@ -1490,44 +1514,61 @@
       <c r="C6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+      <c r="E6" s="18" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>64</v>
+        <v>108</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="23">
-        <v>4</v>
+        <v>110</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>33</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>63</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="33" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="21">
+        <v>4</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="33" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E9" s="18" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1536,9 +1577,12 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" sqref="D3" xr:uid="{E60B603A-EA17-407C-97AF-BC59AA29D1A3}">
       <formula1>"JPG,PNG,TIFF,CSV,JSON,JSONL,Parquet,YOLO TXT,COCO JSON,PyTorch,TensorFlow,folder"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="잘못된 입력" error="목록에서 선택하세요: column / filename / id/key / index" promptTitle="데이터-라벨 매핑 기준" prompt="column / filename / id/key / index 중 하나를 선택하세요" sqref="D6" xr:uid="{E6522DAC-0117-422A-8E76-C31D8100A60A}">
+      <formula1>"column,filename,id/key,index"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1557,13 +1601,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
     </row>
     <row r="2" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -1592,7 +1636,7 @@
       <c r="C3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="21" t="s">
         <v>75</v>
       </c>
       <c r="E3" s="1"/>
@@ -1607,7 +1651,7 @@
       <c r="C4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="23">
+      <c r="D4" s="21">
         <v>0.83</v>
       </c>
       <c r="E4" s="1"/>
@@ -1622,8 +1666,8 @@
       <c r="C5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="23"/>
-      <c r="E5" s="22" t="s">
+      <c r="D5" s="21"/>
+      <c r="E5" s="27" t="s">
         <v>83</v>
       </c>
     </row>
@@ -1637,8 +1681,8 @@
       <c r="C6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="22"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="27"/>
     </row>
     <row r="7" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
@@ -1650,7 +1694,7 @@
       <c r="C7" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="21" t="s">
         <v>76</v>
       </c>
       <c r="E7" s="1"/>
@@ -1665,7 +1709,7 @@
       <c r="C8" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="21">
         <v>0.17</v>
       </c>
       <c r="E8" s="1"/>
@@ -1692,13 +1736,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
     </row>
     <row r="2" spans="1:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -1727,7 +1771,7 @@
       <c r="C3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="21" t="s">
         <v>107</v>
       </c>
       <c r="E3" s="1"/>
@@ -1742,7 +1786,7 @@
       <c r="C4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="21" t="s">
         <v>100</v>
       </c>
       <c r="E4" s="1"/>
@@ -1757,7 +1801,7 @@
       <c r="C5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="21" t="s">
         <v>29</v>
       </c>
       <c r="E5" s="1"/>
@@ -1772,7 +1816,7 @@
       <c r="C6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="21" t="s">
         <v>95</v>
       </c>
       <c r="E6" s="19"/>
@@ -1787,7 +1831,7 @@
       <c r="C7" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="21" t="s">
         <v>96</v>
       </c>
       <c r="E7" s="19"/>
@@ -1802,7 +1846,7 @@
       <c r="C8" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="21" t="s">
         <v>97</v>
       </c>
       <c r="E8" s="2" t="s">
